--- a/schema/PEMB_Extraction_Schema.xlsx
+++ b/schema/PEMB_Extraction_Schema.xlsx
@@ -222,7 +222,7 @@
     <t xml:space="preserve">jurisdiction_ahj</t>
   </si>
   <si>
-    <t xml:space="preserve">Jurisdiction / AHU</t>
+    <t xml:space="preserve">Jurisdiction / AHJ</t>
   </si>
   <si>
     <t xml:space="preserve">city/county</t>
@@ -996,7 +996,7 @@
     <t xml:space="preserve">ASCE 7 Edition</t>
   </si>
   <si>
-    <t xml:space="preserve">ASCE 7-10; 7-16; 7-22</t>
+    <t xml:space="preserve">ASCE 7-10; ASCE 7-16; ASCE 7-22</t>
   </si>
   <si>
     <t xml:space="preserve">ASCE 7-16</t>
@@ -1785,7 +1785,7 @@
     <t xml:space="preserve">Building Use / Occupancy  (rec)</t>
   </si>
   <si>
-    <t xml:space="preserve">Jurisdiction / AHU  (rec)</t>
+    <t xml:space="preserve">Jurisdiction / AHJ  (rec)</t>
   </si>
   <si>
     <t xml:space="preserve">Number of Bays  (rec)</t>
